--- a/assetcore/public/import_templates/05_kho_hang.xlsx
+++ b/assetcore/public/import_templates/05_kho_hang.xlsx
@@ -542,7 +542,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📋 HƯỚNG DẪN IMPORT: Kho hàng (Warehouse)  |  Điền dữ liệu từ hàng 5 trở xuống. Cột đỏ = bắt buộc. Không xóa hàng 2-4.</t>
+          <t>📋 HƯỚNG DẪN IMPORT: Kho hàng (Warehouse)  |  Điền dữ liệu từ HÀNG 6 trở xuống (hàng 5 là ví dụ mẫu, hệ thống bỏ qua). Cột đỏ = bắt buộc. Không xoá/không sửa hàng 1-5. Cột tham chiếu (danh mục, khoa phòng, vị trí, model, nhà cung cấp) điền TÊN, không điền mã.</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Tên vị trí (khớp file 01 / sheet 'Vị trí').</t>
+          <t>Tên vị trí, khớp file 01 / sheet 'Vị trí'. Điền TÊN, KHÔNG điền mã hệ thống.</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Tên khoa phòng chịu trách nhiệm kho (khớp file 01).</t>
+          <t>Tên khoa/phòng chịu trách nhiệm kho, khớp file 01. Điền TÊN, KHÔNG điền mã hệ thống.</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -1599,7 +1599,7 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="F5:F105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="F6:F105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"1,0"</formula1>
     </dataValidation>
   </dataValidations>

--- a/assetcore/public/import_templates/05_kho_hang.xlsx
+++ b/assetcore/public/import_templates/05_kho_hang.xlsx
@@ -1599,7 +1599,7 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="F6:F105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="F6:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"1,0"</formula1>
     </dataValidation>
   </dataValidations>
